--- a/public/inputs/y06-english - input.xlsx
+++ b/public/inputs/y06-english - input.xlsx
@@ -444,7 +444,6 @@
           <t>Unit 1 · Different voices - different times</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -457,7 +456,6 @@
           <t>1.1: What is a prologue?</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -470,7 +468,6 @@
           <t>1.1: 0: Finding out more about flashbacks</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -483,7 +480,6 @@
           <t>1.1: 1: Create voice 4 at the museum</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -496,7 +492,6 @@
           <t>1.1: 2: Create voice 4 at the museum</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -509,7 +504,6 @@
           <t>1.2: Delve into detail</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -522,7 +516,6 @@
           <t>1.3: Focus on technique</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -535,7 +528,6 @@
           <t>1.4: Write a short prologue</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -548,7 +540,6 @@
           <t>1.5: White bears</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -561,7 +552,6 @@
           <t>1.6: Short and long sentences</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -574,7 +564,6 @@
           <t>1.7: Review word classes</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -587,7 +576,6 @@
           <t>1.8: Review dialogue</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -600,7 +588,6 @@
           <t>1.9: Voices</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -613,7 +600,6 @@
           <t>Unit 2 · People in the news</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -626,7 +612,6 @@
           <t>2.1: Making headlines</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -639,7 +624,6 @@
           <t>2.1: 0: Practise reporting</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -652,7 +636,6 @@
           <t>2.1: 1: Write a news article</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -665,7 +648,6 @@
           <t>2.1: 2: Write a news article</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -678,7 +660,6 @@
           <t>2.2: Read all about it</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -691,7 +672,6 @@
           <t>2.3: Layout and purpose</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -704,7 +684,6 @@
           <t>2.4: Report a story</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -717,7 +696,6 @@
           <t>2.5: Explore biographies</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -730,7 +708,6 @@
           <t>2.6: Make a start</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -743,7 +720,6 @@
           <t>2.7: Make a start</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -756,7 +732,6 @@
           <t>2.8: Another life</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -769,7 +744,6 @@
           <t>2.9: Conduct an interview</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -782,7 +756,6 @@
           <t>Unit 3 · Personification and imagery</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -795,7 +768,6 @@
           <t>3.1: The river</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -808,7 +780,6 @@
           <t>3.2: Compare poems</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -821,7 +792,6 @@
           <t>3.3: Look deeper</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -834,7 +804,6 @@
           <t>3.4: Right here was the ocean</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -847,7 +816,6 @@
           <t>3.5: Explore figurative language</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -860,7 +828,6 @@
           <t>3.6: Write your own poem</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -873,7 +840,6 @@
           <t>Unit 4 · Back to the future</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -886,7 +852,6 @@
           <t>4.1: Looking into the future</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -896,10 +861,9 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>4.1: 0: Spelling,punctuation and grammar</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>4.1: 0: Spelling, punctuation and grammar</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -912,7 +876,6 @@
           <t>4.1: 1: Finish your story</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -925,7 +888,6 @@
           <t>4.1: 2: Take part in a readaloudthon</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -938,7 +900,6 @@
           <t>4.2: Step into their shoes</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -951,7 +912,6 @@
           <t>4.3: Useful punctuation and grammar tips</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -964,7 +924,6 @@
           <t>4.4: Begin planning a longer story</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -977,7 +936,6 @@
           <t>4.5: Going back and looking into the future</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -990,7 +948,6 @@
           <t>4.6: Working with voices and moods</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1000,10 +957,9 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>4.7: Working with chapters,paragraphs and connectives</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>4.7: Working with chapters, paragraphs and connectives</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1016,7 +972,6 @@
           <t>4.8: Write paragraphs describing fictional surroundings</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1029,7 +984,6 @@
           <t>4.9: Going forward in time</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1042,7 +996,6 @@
           <t>Unit 5 · The facts of the matter</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1055,7 +1008,6 @@
           <t>5.1: Poles apart</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1068,7 +1020,6 @@
           <t>5.1: 0: A strong viewpoint</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1081,7 +1032,6 @@
           <t>5.1: 1: Pick a side</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1094,7 +1044,6 @@
           <t>5.1: 2: Have a class debate</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1107,7 +1056,6 @@
           <t>5.2: A news report</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1120,7 +1068,6 @@
           <t>5.3: Support a view</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1133,7 +1080,6 @@
           <t>5.4: Express possibility</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1146,7 +1092,6 @@
           <t>5.5: Keep it formal</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1159,7 +1104,6 @@
           <t>5.6: A balanced report</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1172,7 +1116,6 @@
           <t>5.7: Language techniques</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1185,7 +1128,6 @@
           <t>5.8: Present a balanced view</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1198,7 +1140,6 @@
           <t>5.9: Present a balanced view</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1211,7 +1152,6 @@
           <t>Unit 6 · Poetry at play</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1224,7 +1164,6 @@
           <t>6.1: Poetic licence</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1237,7 +1176,6 @@
           <t>6.2: A string of words</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1250,7 +1188,6 @@
           <t>6.3: Patterns and shapes</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1263,7 +1200,6 @@
           <t>6.4: Follow the rules</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1276,7 +1212,6 @@
           <t>6.5: Laugh with limericks</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1289,7 +1224,6 @@
           <t>6.6: Play with words</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1302,7 +1236,6 @@
           <t>Unit 7 · A different medium</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1315,7 +1248,6 @@
           <t>7.1: A multimedia novel</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1328,7 +1260,6 @@
           <t>7.1: 0: Using language</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1341,7 +1272,6 @@
           <t>7.1: 1: Shakespeare alive</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1354,7 +1284,6 @@
           <t>7.1: 2: Write your own play script</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1367,7 +1296,6 @@
           <t>7.2: Language matters</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1380,7 +1308,6 @@
           <t>7.3: Plan and write an illustrated episode</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1393,7 +1320,6 @@
           <t>7.4: Plan and write an illustrated episode</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1406,7 +1332,6 @@
           <t>7.5: Introducing manga</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1419,7 +1344,6 @@
           <t>7.6: Shion</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1432,7 +1356,6 @@
           <t>7.7: Medium matters</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1445,7 +1368,6 @@
           <t>7.8: All the world's a stage</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1458,7 +1380,6 @@
           <t>7.9: What has changed</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1471,7 +1392,6 @@
           <t>Unit 8 · Make it happen</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1484,7 +1404,6 @@
           <t>8.1: Weigh up waste</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1497,7 +1416,6 @@
           <t>8.1: 0: Summarise</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1510,7 +1428,6 @@
           <t>8.1: 1: Create a magazine article</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1523,7 +1440,6 @@
           <t>8.1: 2: Create a magazine article</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1536,7 +1452,6 @@
           <t>8.2: An article to startle</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1549,7 +1464,6 @@
           <t>8.3: Language and features</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1562,7 +1476,6 @@
           <t>8.4: Punctuation with purpose</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1575,7 +1488,6 @@
           <t>8.5: Follow instructions</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1588,7 +1500,6 @@
           <t>8.6: Clauses to clarify</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1601,7 +1512,6 @@
           <t>8.7: Make something</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1614,7 +1524,6 @@
           <t>8.8: Demonstrate</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1627,7 +1536,6 @@
           <t>8.9: Facts and opinions about recycling</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1640,7 +1548,6 @@
           <t>Unit 9 · A moment in time</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1653,7 +1560,6 @@
           <t>9.1: When you look at a painting</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1666,7 +1572,6 @@
           <t>9.2: Poetic form and features</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1679,7 +1584,6 @@
           <t>9.3: There for a moment</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1692,7 +1596,6 @@
           <t>9.4: Features for effect</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1705,7 +1608,6 @@
           <t>9.5: A jewel</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1718,7 +1620,6 @@
           <t>9.6: 'Encapsulate' a moment in time</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
